--- a/perfiles/S.xlsx
+++ b/perfiles/S.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udistritaleduco-my.sharepoint.com/personal/krprietos_udistrital_edu_co/Documents/UDISTRITAL/Calculadora de vigas/perfiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_514D2027883FB33FA7180726F8012D16118A44C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61AE0F06-D850-467D-997A-E4B74BD036D2}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="11_514D2027883FB33FA7180726F8012D16118A44C4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12737ED4-A719-4947-9CC1-0753932C80DF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
